--- a/www/terminologies/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
+++ b/www/terminologies/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
@@ -100,13 +100,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-SERAFINPH|2023.1.0</t>
+    <t>https://smt.esante.gouv.fr/terminologie-SERAFINPH</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R211-ActiviteOperationnelle/FHIR/TRE-R211-ActiviteOperationnelle|20251222120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R211-ActiviteOperationnelle/FHIR/TRE-R211-ActiviteOperationnelle</t>
   </si>
   <si>
     <t>2.1.1.1</t>
@@ -400,7 +400,7 @@
     <t>548</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R266-FamilleActiviteOperationnelleHorsSerafin/FHIR/TRE-R266-FamilleActiviteOperationnelleHorsSerafin|20231215120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R266-FamilleActiviteOperationnelleHorsSerafin/FHIR/TRE-R266-FamilleActiviteOperationnelleHorsSerafin</t>
   </si>
   <si>
     <t>01</t>
